--- a/docs/assets/infraestructura/s2-e2-plan-resultados-pruebas-red.xlsx
+++ b/docs/assets/infraestructura/s2-e2-plan-resultados-pruebas-red.xlsx
@@ -506,7 +506,7 @@
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
     <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="52.83203125" customWidth="1"/>
     <col min="8" max="8" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -787,10 +787,10 @@
         <v>HSTS, X-Content-Type-Options, protección contra framing, Referrer-Policy y Server sin versión</v>
       </c>
       <c r="F11" t="str">
-        <v>Colegio: ninguna cabecera de seguridad y Server: nginx/&lt;versión omitida&gt; (Ubuntu). Academia: solo HSTS (2026-10-24)</v>
+        <v>Colegio: ninguna cabecera de seguridad y Server: nginx/&lt;versión omitida&gt; (Ubuntu). Academia: solo HSTS en la primera medición; tras publicar vercel.json (2026-10-24): X-Content-Type-Options, Referrer-Policy, CSP frame-ancestors, Permissions-Policy y HSTS</v>
       </c>
       <c r="G11" t="str">
-        <v>No conforme</v>
+        <v>No conforme (academia conforme; colegio pendiente)</v>
       </c>
       <c r="H11" t="str">
         <v>Anexo B de S2-E2; acción en R-13</v>
@@ -1518,7 +1518,7 @@
     <col min="6" max="6" width="60.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
     <col min="8" max="8" width="60.83203125" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="51.83203125" customWidth="1"/>
     <col min="10" max="10" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1571,7 +1571,7 @@
         <v>S1 (alta)</v>
       </c>
       <c r="F2" t="str">
-        <v>Corrección en código con 19 pruebas; publicación pendiente por decisión del equipo</v>
+        <v>Corrección con 19 pruebas; frontend y reglas publicados el 2026-10-24 y verificados como visitante sin sesión (listar matrículas pagadas → 403)</v>
       </c>
       <c r="G2" t="str">
         <v>Una línea inválida impedía compilar y nadie verificaba el despliegue</v>
@@ -1580,7 +1580,7 @@
         <v>Publicar solo por CI y verificar el ruleset publicado</v>
       </c>
       <c r="I2" t="str">
-        <v>Abierto</v>
+        <v>Cerrado (2026-10-24)</v>
       </c>
       <c r="J2" t="str">
         <v>R-01 a R-04; NC-01 y NC-02</v>
@@ -1594,7 +1594,7 @@
         <v>2026-10-24</v>
       </c>
       <c r="C3" t="str">
-        <v>Clave de cuenta de servicio y archivos de entorno con credenciales en el repositorio privado (copias ZIP y archivos versionados)</v>
+        <v>Clave de cuenta de servicio y archivos de entorno en el repositorio privado (copias ZIP y archivos versionados)</v>
       </c>
       <c r="D3" t="str">
         <v>Incidente de seguridad: credencial expuesta</v>
@@ -1603,7 +1603,7 @@
         <v>S1 (alta)</v>
       </c>
       <c r="F3" t="str">
-        <v>Retiro de copias iniciado</v>
+        <v>Clave de enero (283b43c3…) eliminada y reemplazada por ddf50bfe…; contraseñas de las cuentas de teachers.json restablecidas; los .env (sin contraseñas) siguen versionados por decisión del equipo</v>
       </c>
       <c r="G3" t="str">
         <v>Copias del proyecto subidas con secretos; control preventivo ausente</v>
@@ -1612,7 +1612,7 @@
         <v>Escaneo de secretos en el CI y lista de revisión de cambios</v>
       </c>
       <c r="I3" t="str">
-        <v>Abierto (rotación pendiente)</v>
+        <v>Cerrado con riesgo residual aceptado (2026-10-24)</v>
       </c>
       <c r="J3" t="str">
         <v>R-05 y R-06; NC-03</v>
@@ -1673,10 +1673,10 @@
         <v>Configuración por defecto</v>
       </c>
       <c r="H5" t="str">
-        <v>Academia: cabeceras agregadas en vercel.json el 2026-10-24, pendientes de publicar. Colegio: plantilla de Nginx de S2-E2 §4.3</v>
+        <v>Academia: cabeceras publicadas con vercel.json y verificadas el 2026-10-24. Colegio: plantilla de Nginx de S2-E2 §4.3</v>
       </c>
       <c r="I5" t="str">
-        <v>En curso</v>
+        <v>Cerrado para la academia; abierto para el colegio</v>
       </c>
       <c r="J5" t="str">
         <v>R-13</v>

--- a/docs/assets/infraestructura/s2-e2-plan-resultados-pruebas-red.xlsx
+++ b/docs/assets/infraestructura/s2-e2-plan-resultados-pruebas-red.xlsx
@@ -8,8 +8,8 @@
     <sheet name="Incidencias" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Pruebas'!A1:H38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Incidencias'!A1:J6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Pruebas'!A1:H40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Incidencias'!A1:J7</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -498,15 +498,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="55.83203125" customWidth="1"/>
-    <col min="3" max="3" width="56.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
     <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="52.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -787,13 +787,13 @@
         <v>HSTS, X-Content-Type-Options, protección contra framing, Referrer-Policy y Server sin versión</v>
       </c>
       <c r="F11" t="str">
-        <v>Colegio: ninguna cabecera de seguridad y Server: nginx/&lt;versión omitida&gt; (Ubuntu). Academia: solo HSTS en la primera medición; tras publicar vercel.json (2026-10-24): X-Content-Type-Options, Referrer-Policy, CSP frame-ancestors, Permissions-Policy y HSTS</v>
+        <v>Primera medición: el colegio sin cabeceras de seguridad y con Server: nginx/&lt;versión omitida&gt; (Ubuntu); la SPA solo con HSTS. Tras los cambios del 2026-10-24: colegio con 5 de 5 cabeceras en la portada, www, /login, la API y los archivos estáticos, y Server: nginx sin versión; SPA con X-Content-Type-Options, Referrer-Policy, CSP frame-ancestors, Permissions-Policy y HSTS</v>
       </c>
       <c r="G11" t="str">
-        <v>No conforme (academia conforme; colegio pendiente)</v>
+        <v>Conforme</v>
       </c>
       <c r="H11" t="str">
-        <v>Anexo B de S2-E2; acción en R-13</v>
+        <v>Anexo B de S2-E2; manual de despliegue §7.2; acción en R-13</v>
       </c>
     </row>
     <row r="12">
@@ -1498,17 +1498,69 @@
         <v>A adjuntar: captura del panel de Wazuh</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>PR-38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>HTTPS de los subdominios de la academia en el VPS</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Cifrado y disponibilidad de la API y la analítica</v>
+      </c>
+      <c r="D39" t="str">
+        <v>curl -sI http://…; curl -s https://api-academia…/health y https://analitica-academia…/health; certbot renew --dry-run</v>
+      </c>
+      <c r="E39" t="str">
+        <v>301 a HTTPS; /health con MySQL conectado; certificado vigente</v>
+      </c>
+      <c r="F39" t="str">
+        <v>301 en ambos; "status":"ok" con MySQL conectado; certificado de Let's Encrypt para los dos subdominios, vence el 2027-01-23; renovación simulada correcta (2026-10-24)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Conforme</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Manual de despliegue §9.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>PR-39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Exposición de la capa de la academia</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Solo Nginx atiende desde afuera y nada responde sin sesión</v>
+      </c>
+      <c r="D40" t="str">
+        <v>ss -lntp en el VPS; curl sin token; OPTIONS con un Origin ajeno</v>
+      </c>
+      <c r="E40" t="str">
+        <v>3001, 8000 y 3306 solo en 127.0.0.1; 401 sin sesión; CORS solo para el origen de la academia</v>
+      </c>
+      <c r="F40" t="str">
+        <v>3001 y 8000 solo en 127.0.0.1 y MySQL con bind-address 127.0.0.1; API 401 en /api/sync/payment y analítica 401 sin sesión; origen de Vercel permitido y origen ajeno rechazado (2026-10-24)</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Conforme</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Manual de despliegue §9.1, §9.4 y §9.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H38"/>
+  <autoFilter ref="A1:H40"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1519,7 +1571,7 @@
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
     <col min="8" max="8" width="60.83203125" customWidth="1"/>
     <col min="9" max="9" width="51.83203125" customWidth="1"/>
-    <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1673,10 +1725,10 @@
         <v>Configuración por defecto</v>
       </c>
       <c r="H5" t="str">
-        <v>Academia: cabeceras publicadas con vercel.json y verificadas el 2026-10-24. Colegio: plantilla de Nginx de S2-E2 §4.3</v>
+        <v>Academia: cabeceras publicadas con vercel.json. Colegio: fragmento de Nginx con 5 cabeceras y server_tokens off, aplicado y verificado el 2026-10-24 (S2-E2 §4.3)</v>
       </c>
       <c r="I5" t="str">
-        <v>Cerrado para la academia; abierto para el colegio</v>
+        <v>Cerrado (2026-10-24)</v>
       </c>
       <c r="J5" t="str">
         <v>R-13</v>
@@ -1714,10 +1766,42 @@
         <v>R-11 y R-14</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>INC-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>La sincronización con la API del VPS respondió 500 a las 20:40 y 20:42, y la migración que lo corregía quedó bloqueada más de 20 minutos</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Incidente de disponibilidad e integridad de la réplica relacional; sin exposición de datos</v>
+      </c>
+      <c r="E7" t="str">
+        <v>S3 (media)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Detección: consola del panel ([sync] … respondió 500) y registros de PM2 (Data truncated for column 'turno'). Contención: API y analítica detenidas desde otra ventana, lo que liberó la transacción abierta</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Tres defectos de la base: etiqueta mañana dañada desde junio, rutinas del VPS con otra collation y transacción abierta tras errores de clase 01 (E4 §2.8)</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Reproducir cada falla en una réplica antes de corregir; migrar con los servicios detenidos y una espera máxima de 60 s; la API cierra la conexión ante un error</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Cerrado (2026-10-24 22:11)</v>
+      </c>
+      <c r="J7" t="str">
+        <v>R-27 y R-28; ACT-16 y ACT-17</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J7"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>